--- a/templates/说明书审核清单-母版-20260818.xlsx
+++ b/templates/说明书审核清单-母版-20260818.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>说明书审核清单 · 母版 v2.0（2026-08-18）</t>
+          <t>说明书审核清单 · 母版 v2.1（2026-08-18）</t>
         </is>
       </c>
     </row>
@@ -446,136 +446,123 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>三级编号 Lx.y.z = 层(L1-L9) + 子类(Lx.y) + 细项(Lx.y.z)；每项带「适用法域」：通用 / 具体法域（多值用·分隔）/ 国别特有项标国名。</t>
+          <t>三级编号 Lx.y.z；每项带「适用法域」；某国清单=通用+命中法域项。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>某国清单 = 通用项 + 该国命中法域项，不再 120 项一刀切。</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>维护规则：增删只改母版→同步衍生视图（单向）；归属拿不准默认 L4；法域拿不准标「通用」+「需当地律师确认」。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>—— 维护规则 ——</t>
-        </is>
-      </c>
+      <c r="A6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>· 增删只改母版 → 同步衍生视图（单向），禁止反向。</t>
+          <t>审核级别：细审(首次)=该国本土化清单 | 粗审(升级)=L4层本土化 | 升级快检=8项。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>· 新增子类 X.N；新增细项编号 X.N.(顺延)；停用标「（已停用）」不物理删除。</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>· 归属拿不准默认放 L4；法域归属拿不准优先标「通用」+「需当地律师确认」。</t>
+          <t>—— 变更记录 ——</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>版本</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>变更</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>作者</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>—— 审核级别 ——</t>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>从首次审核清单 Excel 抽取全部 120 项 + 升级快检 8 项，固化为母版流程文档（单源真相）</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>合规中枢</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>细审(首次)=该国本土化清单 | 粗审(升级)=L4层本土化细项 | 升级快检=8项</t>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>三级编号（Lx.y.z）+ 细项本土化：加「适用法域」列，拆通用/本土，判定标准去多国混写；新增附录 A（法域映射）/附录 B（认证制度速查表）；每国清单改为「通用 + 命中法域」过滤生成，废弃原「领域代表」未填列</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>合规中枢</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>—— 变更记录 ——</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>版本</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>变更</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>作者</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>从首次审核清单 Excel 抽取全部 120 项 + 升级快检 8 项，固化为母版流程文档（单源真相）</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>合规中枢</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>三级编号（Lx.y.z）+ 细项本土化：加「适用法域」列，拆通用/本土，判定标准去多国混写；新增附录 A（法域映射）/附录 B（认证制度速查表）；每国清单改为「通用 + 命中法域」过滤生成，废弃原「领域代表」未填列</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>附录 B2 查证回填（法规库）：东盟各国法定保修无固定年限（缺陷责任）、数据法多无明确儿童年龄门槛（越南 PDPD 16 岁除外）、SAR 认可口径 ICNIRP 10g 基准待认证机构确认</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>合规中枢</t>
         </is>
@@ -5782,15 +5769,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6019,17 +6006,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>无统一年限（CPA 2019）</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18 岁（DPDP 待核）</t>
+          <t>18 岁（DPDP）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DPDP 待核</t>
+          <t>DPDP（18 岁下监护人同意，待核）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6061,7 +6048,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>10g（ICNIRP，认可口径待确认）</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6071,17 +6058,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UUPK（待核）</t>
+          <t>无固定年限（UUPK 8/1999）</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>未设明确门槛</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PDP 待核</t>
+          <t>无明确门槛（PDP）</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6113,7 +6100,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>10g（ICNIRP，认可口径待确认）</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6123,17 +6110,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>无固定年限（59/2010/QH12）</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16 岁（PDPD 待核）</t>
+          <t>16 岁（PDPD）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>PDPD 待核</t>
+          <t>PDPD（16 岁下监护人同意）</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6165,7 +6152,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>10g（ICNIRP，认可口径待确认）</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6175,17 +6162,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>无固定年限（消保法 1979）</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>未设明确门槛</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PDPA 待核</t>
+          <t>无明确门槛（PDPA）</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6217,7 +6204,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>10g（ICNIRP，认可口径待确认）</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6227,17 +6214,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>Lemon Law 6 个月（CPFTA 2003）</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13 岁（PDPA 待核）</t>
+          <t>未设明确门槛</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PDPA 待核</t>
+          <t>无明确门槛（PDPA）</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6269,7 +6256,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>10g（ICNIRP，认可口径待确认）</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6279,17 +6266,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>无固定年限（CPA 1999）</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>未设明确门槛</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PDPA 待核</t>
+          <t>无明确门槛（PDPA）</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6331,17 +6318,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ACL/Reg 90（待核）</t>
+          <t>ACL 无固定年限（可接受质量）</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13 岁（APPs 待核）</t>
+          <t>未设明确门槛</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>APPs 待核</t>
+          <t>无明确门槛（APPs）</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6373,7 +6360,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>10g（ICNIRP，认可口径待确认）</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6383,17 +6370,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>无固定年限（消保法）</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>未设明确门槛</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>个资法 待核</t>
+          <t>无明确门槛（个资法）</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6425,7 +6412,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>10g（ICNIRP，认可口径待确认）</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6435,17 +6422,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>无固定年限（RA 7394）</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>待核</t>
+          <t>未设明确门槛</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>数据隐私法 待核</t>
+          <t>无明确门槛（数据隐私法）</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
